--- a/template/billeterie.xlsx
+++ b/template/billeterie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/support/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33ADD0C-3E0B-5C47-97AB-72F728D90772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764A77D4-A518-DC4E-AD10-3DA19D87FD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11400" yWindow="1060" windowWidth="28040" windowHeight="15560" xr2:uid="{DF9C8B8D-C7CB-4E48-96BB-D75396ED2350}"/>
+    <workbookView xWindow="2200" yWindow="1060" windowWidth="28040" windowHeight="15560" xr2:uid="{DF9C8B8D-C7CB-4E48-96BB-D75396ED2350}"/>
   </bookViews>
   <sheets>
     <sheet name="liste" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Équipe</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Membres</t>
   </si>
   <si>
-    <t>Lien Spiceworks</t>
-  </si>
-  <si>
     <t>David P.&lt;br/&gt;Christophe M.&lt;br/&gt;Dereck D.&lt;br/&gt;Justin Le.</t>
   </si>
   <si>
@@ -87,6 +84,33 @@
   </si>
   <si>
     <t>[Jira Équipe 4](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E4/queues/custom/57?atlOrigin=eyJpIjoiODNhYjNlY2RmZDUxNDdlNmI2YTQxYzIwYTg5MzEzYWMiLCJwIjoiaiJ9)</t>
+  </si>
+  <si>
+    <t>Lien Jira</t>
+  </si>
+  <si>
+    <t>Lien Notion</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 1](https://www.notion.so/03e7425d2af482b69c6401b5a379cef3?v=12a7425d2af483f6858a08987032dcd9&amp;source=copy_link)</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 2](https://www.notion.so/4667425d2af48364bf1381c407028643?v=8947425d2af4831e9fa688a1273e6dab&amp;source=copy_link)</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 3](https://www.notion.so/3287425d2af48007914acfba3d3070c6?v=3287425d2af4810eaafc000cd6d08627&amp;source=copy_link)</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 4](https://www.notion.so/3287425d2af4808791afce1e62320da8?v=3287425d2af4818cab44000cd42c6cce&amp;source=copy_link)</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 5](https://www.notion.so/3287425d2af480beb74ffc95a5cb4406?v=3287425d2af48194a92a000cf1389f96&amp;source=copy_link)</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 6](https://www.notion.so/3287425d2af48047bd9fd8e9c1f04a0d?v=3287425d2af481fe88db000cbeea1f2f&amp;source=copy_link)</t>
+  </si>
+  <si>
+    <t>[Notion Équipe 7](https://www.notion.so/3287425d2af480118c2cee7740a296d9?v=3287425d2af48139a914000c61f73831&amp;source=copy_link)</t>
   </si>
 </sst>
 </file>
@@ -470,14 +494,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D45217-176D-3B43-A394-6BB062C4D536}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="2" max="2" width="55.6640625" customWidth="1"/>
     <col min="3" max="3" width="33.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -485,84 +509,108 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/template/billeterie.xlsx
+++ b/template/billeterie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/support/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764A77D4-A518-DC4E-AD10-3DA19D87FD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEA268A-9136-0C48-91DB-8B8EE4A6F41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="1060" windowWidth="28040" windowHeight="15560" xr2:uid="{DF9C8B8D-C7CB-4E48-96BB-D75396ED2350}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Équipe</t>
   </si>
@@ -63,30 +63,6 @@
   </si>
   <si>
     <t>Nathan G.&lt;br/&gt;Mavrick R.&lt;br/&gt;Henri L.</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 1](https://cegepvicto.atlassian.net/jira/servicedesk/projects/SUP1/queues/custom/1?atlOrigin=eyJpIjoiYjI1ODU0YTFkYjllNGE0NGI4MjZiZDI5YjM5MTFiMmUiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 2](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E2/queues/custom/9?atlOrigin=eyJpIjoiZTkwYTUyMzg2NDU4NDQwZmFkMDI1YWJjYTZhOGY2YmYiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 3](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E3/queues/custom/49?atlOrigin=eyJpIjoiMGNlM2RiYjBiYjUwNDA1YWFmMTkwNjJjNWVhNGRlY2QiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 7](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E7/queues/custom/81?atlOrigin=eyJpIjoiY2VkNTRhOTAzMmE2NDlmNGFhZGJmZDg2YTI3NDc5YzgiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 6](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E6/queues/custom/73?atlOrigin=eyJpIjoiMGU3ZWE4Yjk2YmFmNDAwMGIzNzkxMjZiZDM3NGQyYTMiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 5](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E5/queues/custom/65?atlOrigin=eyJpIjoiNzQ2MzdmYmE3M2FkNDg0ZDhhYWE4ZWM1NGM5NDIyNjEiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>[Jira Équipe 4](https://cegepvicto.atlassian.net/jira/servicedesk/projects/E4/queues/custom/57?atlOrigin=eyJpIjoiODNhYjNlY2RmZDUxNDdlNmI2YTQxYzIwYTg5MzEzYWMiLCJwIjoiaiJ9)</t>
-  </si>
-  <si>
-    <t>Lien Jira</t>
   </si>
   <si>
     <t>Lien Notion</t>
@@ -494,14 +470,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D45217-176D-3B43-A394-6BB062C4D536}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="55.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,13 +484,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -523,13 +495,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -537,13 +506,10 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -551,13 +517,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -565,13 +528,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -581,11 +541,8 @@
       <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -593,13 +550,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -607,10 +561,7 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
